--- a/data/lillestrom_overall_summary.xlsx
+++ b/data/lillestrom_overall_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JES\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F63D40-A66F-4192-B3F1-D391A6843688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47FAC88-CBC3-478B-831F-E6F8B8547062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="793" yWindow="707" windowWidth="13900" windowHeight="12406" xr2:uid="{D7FB886E-A0E9-4A18-892F-256865980117}"/>
+    <workbookView xWindow="-1360" yWindow="2493" windowWidth="13900" windowHeight="12407" xr2:uid="{D7FB886E-A0E9-4A18-892F-256865980117}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="43">
   <si>
     <t>Nedbørfelt</t>
   </si>
@@ -153,6 +153,21 @@
   </si>
   <si>
     <t>19 to 58</t>
+  </si>
+  <si>
+    <t>64*</t>
+  </si>
+  <si>
+    <t>20*</t>
+  </si>
+  <si>
+    <t>24*</t>
+  </si>
+  <si>
+    <t>23*</t>
+  </si>
+  <si>
+    <t>Nei†</t>
   </si>
 </sst>
 </file>
@@ -860,8 +875,8 @@
       <c r="D14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="3">
-        <v>64</v>
+      <c r="E14" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>20</v>
@@ -883,8 +898,8 @@
       <c r="D15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="3">
-        <v>20</v>
+      <c r="E15" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>21</v>
@@ -1130,6 +1145,21 @@
       <c r="B26" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
@@ -1138,6 +1168,21 @@
       <c r="B27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="C27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28" s="3" t="s">
@@ -1149,7 +1194,16 @@
       <c r="C28" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="D28" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1163,7 +1217,16 @@
       <c r="C29" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="D29" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>17</v>
       </c>
     </row>

--- a/data/lillestrom_overall_summary.xlsx
+++ b/data/lillestrom_overall_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JES\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47FAC88-CBC3-478B-831F-E6F8B8547062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD32A4F-262C-422D-AF1B-DDBAB7A56C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1360" yWindow="2493" windowWidth="13900" windowHeight="12407" xr2:uid="{D7FB886E-A0E9-4A18-892F-256865980117}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25787" windowHeight="15467" xr2:uid="{D7FB886E-A0E9-4A18-892F-256865980117}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>10 to 20</t>
-  </si>
-  <si>
     <t>3 to 40</t>
   </si>
   <si>
@@ -168,6 +165,9 @@
   </si>
   <si>
     <t>Nei†</t>
+  </si>
+  <si>
+    <t>8 to 19</t>
   </si>
 </sst>
 </file>
@@ -583,7 +583,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.5">
@@ -594,19 +594,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -617,19 +617,19 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
@@ -640,10 +640,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>17</v>
@@ -663,10 +663,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>17</v>
@@ -686,19 +686,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -709,19 +709,19 @@
         <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
@@ -732,10 +732,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>17</v>
@@ -755,10 +755,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>17</v>
@@ -778,19 +778,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.5">
@@ -801,19 +801,19 @@
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.5">
@@ -824,10 +824,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>17</v>
@@ -847,10 +847,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>17</v>
@@ -870,19 +870,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.5">
@@ -893,19 +893,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
@@ -916,10 +916,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>17</v>
@@ -939,10 +939,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>17</v>
@@ -962,19 +962,19 @@
         <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.5">
@@ -985,19 +985,19 @@
         <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
@@ -1008,10 +1008,10 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>17</v>
@@ -1031,10 +1031,10 @@
         <v>9</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>17</v>
@@ -1054,19 +1054,19 @@
         <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.5">
@@ -1077,19 +1077,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
@@ -1100,10 +1100,10 @@
         <v>10</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>17</v>
@@ -1123,10 +1123,10 @@
         <v>9</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>17</v>
@@ -1146,19 +1146,19 @@
         <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.5">
@@ -1169,19 +1169,19 @@
         <v>7</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.5">
@@ -1192,10 +1192,10 @@
         <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>17</v>
@@ -1215,10 +1215,10 @@
         <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>17</v>
